--- a/simulation_data/monday_evening.xlsx
+++ b/simulation_data/monday_evening.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>system_time_min</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>2.133513300574315</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>2.534952292563114</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>3.315779159014653</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>4.864952526132468</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>4.008709945512336</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>2.716141128867163</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>2.145073566810527</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>3.331575634708662</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>5.543222671394687</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>3.413106163954637</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>1.265615903219343</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>3.505943420914025</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>2.68767316804417</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>3.091249092485168</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>2.2112064810552</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>3.294237207240085</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>1.950127684111263</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>2.662251714858611</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>0.7310627619644402</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>1.24512199680845</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>2.48844442786644</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>2.614199760857267</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>3.856356572338836</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>2.218607839031174</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>3.318090418877304</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>2.969066300650959</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>0.8405412390627566</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>1.987364961852998</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>0.8047286256925367</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>3.008641183423246</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>1.369951575864557</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>1.924385421071703</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>0.9438357542088813</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>3.114417507631722</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>2.315111317039701</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>2.107106245810548</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>2.841302107061406</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>1.25731080084759</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>2.047202737434735</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>1.486526256400259</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>2.480359203833477</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>3.222197931059081</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>1.801454900884714</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>1.796252874842953</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>2.67664556841388</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>3.895432703842404</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>2.594757433925228</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>4.341379478237018</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>2.214297308185381</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>1.900004311088321</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>1.868305119123718</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>4.819552376003731</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>2.78959811990231</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>2.327982208617767</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>1.868115077443095</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>4.853717865754705</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2116,6 +2401,11 @@
       </c>
       <c r="G58" t="n">
         <v>4.625938200545341</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
       </c>
     </row>
   </sheetData>
